--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>91</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>112</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>114</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>140</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>123</v>
+        <v>119</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>168</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>119</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>180</v>
+        <v>186</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>149</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>185</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>180</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>161</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>155</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>138</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>123</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>97</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>149</v>
+        <v>208</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>208</v>
+        <v>216</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>58</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>216</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>219</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>200</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>33</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>162</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>143</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>164</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>182</v>
+        <v>197</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>197</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>164</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>150</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>134</v>
+        <v>125</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>119</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>105</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>97</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>92</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>130</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>139</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>159</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>161</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>198</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>174</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>193</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>158</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>144</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>184</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>143</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>112</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -558,7 +558,7 @@
         </is>
       </c>
       <c r="D3" s="6" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">

--- a/output/serbia.xlsx
+++ b/output/serbia.xlsx
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
@@ -610,7 +610,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1">
